--- a/data/Tonor/Mar/Sp&Sd.xlsx
+++ b/data/Tonor/Mar/Sp&Sd.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\09-04-26\Sp-sd\AA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\buybox\data\Tonor\Mar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE6976FD-0C45-45AB-A131-3181BAB24BB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E42B53-A6ED-4B84-9A62-836A87F1FAA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{C2EB3544-0B30-4B5A-9817-98DE85FBF6BC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{C2EB3544-0B30-4B5A-9817-98DE85FBF6BC}"/>
   </bookViews>
   <sheets>
     <sheet name="SP" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10931" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11179" uniqueCount="83">
   <si>
     <t>Brand</t>
   </si>
@@ -286,6 +286,12 @@
   </si>
   <si>
     <t>B0BG8CJXHH</t>
+  </si>
+  <si>
+    <t>Ton_Condenser_TC-777_SBV_KT</t>
+  </si>
+  <si>
+    <t>Ton_Dynamic_K1_SBV_KT</t>
   </si>
 </sst>
 </file>
@@ -645,7 +651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51EF6D63-3663-4E20-A7FC-263D078FDDB8}">
-  <dimension ref="A1:I1702"/>
+  <dimension ref="A1:I1764"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="21.88671875" customWidth="1"/>
@@ -50006,6 +50012,1804 @@
         <v>0</v>
       </c>
       <c r="I1702" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1703" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1703" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1703" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1703" s="1">
+        <v>245</v>
+      </c>
+      <c r="E1703" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1703" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1703" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1703" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1703" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1704" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1704" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1704" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1704" s="1">
+        <v>382</v>
+      </c>
+      <c r="E1704" s="1">
+        <v>1</v>
+      </c>
+      <c r="F1704" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1704" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1704" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1704" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1705" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1705" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1705" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1705" s="1">
+        <v>268</v>
+      </c>
+      <c r="E1705" s="1">
+        <v>1</v>
+      </c>
+      <c r="F1705" s="2">
+        <v>8.48</v>
+      </c>
+      <c r="G1705" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1705" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1705" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1706" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1706" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1706" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1706" s="1">
+        <v>238</v>
+      </c>
+      <c r="E1706" s="1">
+        <v>2</v>
+      </c>
+      <c r="F1706" s="2">
+        <v>39.57</v>
+      </c>
+      <c r="G1706" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1706" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1706" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1707" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1707" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1707" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1707" s="1">
+        <v>302</v>
+      </c>
+      <c r="E1707" s="1">
+        <v>1</v>
+      </c>
+      <c r="F1707" s="2">
+        <v>26.01</v>
+      </c>
+      <c r="G1707" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1707" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1707" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1708" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1708" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1708" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1708" s="1">
+        <v>266</v>
+      </c>
+      <c r="E1708" s="1">
+        <v>2</v>
+      </c>
+      <c r="F1708" s="2">
+        <v>25.03</v>
+      </c>
+      <c r="G1708" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1708" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1708" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1709" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1709" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1709" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1709" s="1">
+        <v>247</v>
+      </c>
+      <c r="E1709" s="1">
+        <v>2</v>
+      </c>
+      <c r="F1709" s="2">
+        <v>42.4</v>
+      </c>
+      <c r="G1709" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1709" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1709" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1710" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1710" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1710" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1710" s="1">
+        <v>268</v>
+      </c>
+      <c r="E1710" s="1">
+        <v>2</v>
+      </c>
+      <c r="F1710" s="2">
+        <v>35.33</v>
+      </c>
+      <c r="G1710" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1710" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1710" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1711" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1711" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1711" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1711" s="1">
+        <v>236</v>
+      </c>
+      <c r="E1711" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1711" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1711" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1711" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1711" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1712" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1712" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1712" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1712" s="1">
+        <v>167</v>
+      </c>
+      <c r="E1712" s="1">
+        <v>1</v>
+      </c>
+      <c r="F1712" s="2">
+        <v>36.15</v>
+      </c>
+      <c r="G1712" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1712" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1712" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1713" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1713" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1713" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1713" s="1">
+        <v>350</v>
+      </c>
+      <c r="E1713" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1713" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1713" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1713" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1713" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1714" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1714" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1714" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1714" s="1">
+        <v>405</v>
+      </c>
+      <c r="E1714" s="1">
+        <v>1</v>
+      </c>
+      <c r="F1714" s="2">
+        <v>44.94</v>
+      </c>
+      <c r="G1714" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1714" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1714" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1715" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1715" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1715" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1715" s="1">
+        <v>347</v>
+      </c>
+      <c r="E1715" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1715" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1715" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1715" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1715" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1716" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1716" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1716" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1716" s="1">
+        <v>3042</v>
+      </c>
+      <c r="E1716" s="1">
+        <v>3</v>
+      </c>
+      <c r="F1716" s="2">
+        <v>77.040000000000006</v>
+      </c>
+      <c r="G1716" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1716" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1716" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1717" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1717" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1717" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1717" s="1">
+        <v>127</v>
+      </c>
+      <c r="E1717" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1717" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1717" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1717" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1717" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1718" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1718" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1718" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1718" s="1">
+        <v>63</v>
+      </c>
+      <c r="E1718" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1718" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1718" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1718" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1718" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1719" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1719" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1719" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1719" s="1">
+        <v>72</v>
+      </c>
+      <c r="E1719" s="1">
+        <v>2</v>
+      </c>
+      <c r="F1719" s="2">
+        <v>61.61</v>
+      </c>
+      <c r="G1719" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1719" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1719" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1720" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1720" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1720" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1720" s="1">
+        <v>63</v>
+      </c>
+      <c r="E1720" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1720" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1720" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1720" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1720" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1721" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1721" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1721" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1721" s="1">
+        <v>132</v>
+      </c>
+      <c r="E1721" s="1">
+        <v>1</v>
+      </c>
+      <c r="F1721" s="2">
+        <v>34.729999999999997</v>
+      </c>
+      <c r="G1721" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1721" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1721" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1722" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1722" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1722" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1722" s="1">
+        <v>334</v>
+      </c>
+      <c r="E1722" s="1">
+        <v>1</v>
+      </c>
+      <c r="F1722" s="2">
+        <v>2.21</v>
+      </c>
+      <c r="G1722" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1722" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1722" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1723" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1723" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1723" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1723" s="1">
+        <v>380</v>
+      </c>
+      <c r="E1723" s="1">
+        <v>4</v>
+      </c>
+      <c r="F1723" s="2">
+        <v>63.66</v>
+      </c>
+      <c r="G1723" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1723" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1723" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1724" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1724" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1724" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1724" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1724" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1724" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1724" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1724" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1724" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1725" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1725" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1725" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1725" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1725" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1725" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1725" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1725" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1725" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1726" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1726" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1726" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1726" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1726" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1726" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1726" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1726" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1726" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1727" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1727" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1727" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1727" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1727" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1727" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1727" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1727" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1727" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1728" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1728" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1728" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1728" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1728" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1728" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1728" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1728" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1728" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1729" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1729" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1729" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1729" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1729" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1729" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1729" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1729" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1729" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1730" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1730" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1730" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1730" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1730" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1730" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1730" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1730" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1730" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1731" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1731" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1731" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1731" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1731" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1731" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1731" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1731" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1731" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1732" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1732" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1732" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1732" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1732" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1732" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1732" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1732" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1732" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1733" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1733" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1733" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1733" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1733" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1733" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1733" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1733" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1733" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1734" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1734" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1734" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1734" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1734" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1734" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1734" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1734" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1734" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1735" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1735" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1735" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1735" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1735" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1735" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1735" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1735" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1735" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1736" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1736" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1736" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1736" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1736" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1736" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1736" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1736" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1736" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1737" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1737" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1737" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1737" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1737" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1737" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1737" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1737" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1737" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1738" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1738" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1738" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1738" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1738" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1738" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1738" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1738" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1738" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1739" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1739" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1739" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1739" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1739" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1739" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1739" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1739" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1739" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1739" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1740" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1740" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1740" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1740" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1740" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1740" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1740" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1740" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1740" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1740" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1741" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1741" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1741" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1741" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1741" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1741" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1741" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1741" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1741" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1741" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1742" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1742" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1742" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1742" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1742" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1742" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1742" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1742" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1742" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1742" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1743" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1743" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1743" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1743" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1743" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1743" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1743" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1743" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1743" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1743" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1744" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1744" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1744" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1744" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1744" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1744" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1744" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1744" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1744" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1744" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1745" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1745" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1745" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1745" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1745" s="1">
+        <v>4234</v>
+      </c>
+      <c r="E1745" s="1">
+        <v>11</v>
+      </c>
+      <c r="F1745" s="2">
+        <v>261.83999999999997</v>
+      </c>
+      <c r="G1745" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1745" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1746" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1746" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1746" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1746" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1746" s="1">
+        <v>416</v>
+      </c>
+      <c r="E1746" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1746" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1746" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1746" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1746" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1747" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1747" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1747" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1747" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1747" s="1">
+        <v>379</v>
+      </c>
+      <c r="E1747" s="1">
+        <v>2</v>
+      </c>
+      <c r="F1747" s="2">
+        <v>34.68</v>
+      </c>
+      <c r="G1747" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1747" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1747" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1748" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1748" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1748" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1748" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1748" s="1">
+        <v>225</v>
+      </c>
+      <c r="E1748" s="1">
+        <v>4</v>
+      </c>
+      <c r="F1748" s="2">
+        <v>36.46</v>
+      </c>
+      <c r="G1748" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1748" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1749" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1749" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1749" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1749" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1749" s="1">
+        <v>204</v>
+      </c>
+      <c r="E1749" s="1">
+        <v>1</v>
+      </c>
+      <c r="F1749" s="2">
+        <v>31.01</v>
+      </c>
+      <c r="G1749" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1749" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1749" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1750" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1750" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1750" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1750" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1750" s="1">
+        <v>638</v>
+      </c>
+      <c r="E1750" s="1">
+        <v>1</v>
+      </c>
+      <c r="F1750" s="2">
+        <v>33.36</v>
+      </c>
+      <c r="G1750" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1750" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1750" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1751" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1751" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1751" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1751" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1751" s="1">
+        <v>192</v>
+      </c>
+      <c r="E1751" s="1">
+        <v>3</v>
+      </c>
+      <c r="F1751" s="2">
+        <v>116.6</v>
+      </c>
+      <c r="G1751" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1751" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1751" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1752" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1752" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1752" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1752" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1752" s="1">
+        <v>380</v>
+      </c>
+      <c r="E1752" s="1">
+        <v>2</v>
+      </c>
+      <c r="F1752" s="2">
+        <v>88.87</v>
+      </c>
+      <c r="G1752" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1752" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1752" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1753" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1753" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1753" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1753" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1753" s="1">
+        <v>106</v>
+      </c>
+      <c r="E1753" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1753" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1753" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1753" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1753" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1754" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1754" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1754" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1754" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1754" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1754" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1754" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1754" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1754" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1755" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1755" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1755" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1755" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1755" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1755" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1755" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1755" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1755" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1755" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1756" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1756" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1756" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1756" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1756" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1756" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1756" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1756" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1756" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1756" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1757" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1757" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1757" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1757" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1757" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1757" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1757" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1757" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1757" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1757" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1758" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1758" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1758" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1758" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1758" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1758" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1758" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1758" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1758" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1758" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1759" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1759" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1759" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1759" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1759" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1759" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1759" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1759" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1759" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1759" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1760" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1760" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1760" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1760" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1760" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1760" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1760" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1760" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1760" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1760" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1761" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1761" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1761" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1761" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1761" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1761" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1761" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1761" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1761" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1762" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1762" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1762" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1762" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1762" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1762" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1762" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1762" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1762" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1763" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1763" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1763" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1763" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1763" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1763" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1763" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1763" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1763" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1764" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1764" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1764" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1764" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1764" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1764" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1764" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1764" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1764" t="s">
         <v>9</v>
       </c>
     </row>
